--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1953,7 +1953,7 @@
         <v>136298543</v>
       </c>
       <c r="B14" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1953,7 +1953,7 @@
         <v>136298543</v>
       </c>
       <c r="B14" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1953,7 +1953,7 @@
         <v>136298543</v>
       </c>
       <c r="B14" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1953,7 +1953,7 @@
         <v>136298543</v>
       </c>
       <c r="B14" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1620,48 +1620,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7116630</v>
+        <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>91394</v>
+        <v>93449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2051</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Haftaheden, sydväst Granukölen, Dlr</t>
+          <t>Haftahedarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438877</v>
+        <v>438577</v>
       </c>
       <c r="R11" t="n">
-        <v>6702543</v>
+        <v>6703735</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1685,12 +1694,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2008-10-31</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1701,36 +1720,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>sandtallskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7116630</t>
+          <t>https://artportalen.se/Sighting/136943665</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>562885</v>
+        <v>7116630</v>
       </c>
       <c r="B12" t="n">
-        <v>93213</v>
+        <v>91394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,37 +1752,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>2051</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Haftahedarna (Svenmyran), Dlr</t>
+          <t>Haftaheden, sydväst Granukölen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438883</v>
+        <v>438877</v>
       </c>
       <c r="R12" t="n">
-        <v>6702551</v>
+        <v>6702543</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1792,17 +1806,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2006-10-11</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2006-10-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Inv. av Karin Runesson och Sebastian Kirppu, på uppdrag av Länsstyrelsen Dalarna.</t>
+          <t>2008-10-31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,75 +1825,71 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Sandmark, lavrik. Beståndsålder 100- 150. Mkt välgallrat och likåldrigt.</t>
+          <t>sandtallskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Uno Skog</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Åtgärdsprogram för hotade arter</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/562885</t>
+          <t>https://artportalen.se/Sighting/7116630</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7116629</v>
+        <v>562885</v>
       </c>
       <c r="B13" t="n">
-        <v>93197</v>
+        <v>93213</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Haftaheden, sydväst Granukölen, Dlr</t>
+          <t>Haftahedarna (Svenmyran), Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438877</v>
+        <v>438883</v>
       </c>
       <c r="R13" t="n">
-        <v>6702543</v>
+        <v>6702551</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1908,12 +1913,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2008-05-01</t>
+          <t>2006-10-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2008-10-31</t>
+          <t>2006-10-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Inv. av Karin Runesson och Sebastian Kirppu, på uppdrag av Länsstyrelsen Dalarna.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,71 +1937,75 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>sandtallskog</t>
+          <t>Sandmark, lavrik. Beståndsålder 100- 150. Mkt välgallrat och likåldrigt.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Via Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7116629</t>
+          <t>https://artportalen.se/Sighting/562885</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136298543</v>
+        <v>7116629</v>
       </c>
       <c r="B14" t="n">
-        <v>98221</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Haftahedarna, Dlr</t>
+          <t>Haftaheden, sydväst Granukölen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438790</v>
+        <v>438877</v>
       </c>
       <c r="R14" t="n">
-        <v>6702633</v>
+        <v>6702543</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2015,22 +2029,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:17</t>
+          <t>2008-05-01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:17</t>
+          <t>2008-10-31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,20 +2045,258 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>sandtallskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7116629</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136944413</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56739</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Haftahedarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>438749</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6702897</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ko och kalv</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136944413</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136298543</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98221</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Haftahedarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>438790</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6702633</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Malung</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136298543</t>
         </is>
@@ -2075,6 +2317,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>136944413</v>
       </c>
       <c r="B15" t="n">
-        <v>56739</v>
+        <v>56752</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>136944413</v>
       </c>
       <c r="B15" t="n">
-        <v>56752</v>
+        <v>56754</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>136944413</v>
       </c>
       <c r="B15" t="n">
-        <v>56754</v>
+        <v>56764</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>136944413</v>
       </c>
       <c r="B15" t="n">
-        <v>56764</v>
+        <v>56765</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/S 649-2026 artfynd.xlsx
+++ b/artfynd/S 649-2026 artfynd.xlsx
@@ -1623,7 +1623,7 @@
         <v>136943665</v>
       </c>
       <c r="B11" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>136944413</v>
       </c>
       <c r="B15" t="n">
-        <v>56765</v>
+        <v>56768</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
